--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="42">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,49 +25,52 @@
     <t>ZONA</t>
   </si>
   <si>
+    <t>EN PROCESO DE VENTA</t>
+  </si>
+  <si>
+    <t>VENDIDOS CON PRECIO</t>
+  </si>
+  <si>
+    <t>PROMOS</t>
+  </si>
+  <si>
+    <t>CORTESÍAS</t>
+  </si>
+  <si>
+    <t>PRECIO $1</t>
+  </si>
+  <si>
+    <t>ABONOS VENDIDOS</t>
+  </si>
+  <si>
+    <t>ABONOS PROMOS</t>
+  </si>
+  <si>
+    <t>ABONOS CORTESÍAS</t>
+  </si>
+  <si>
+    <t>ABONOS PRECIO $1</t>
+  </si>
+  <si>
+    <t>PAQUETES</t>
+  </si>
+  <si>
+    <t>PAQUETES CORTESIAS</t>
+  </si>
+  <si>
+    <t>PAQUETES PRECIO $1</t>
+  </si>
+  <si>
+    <t>PROMOCIONES</t>
+  </si>
+  <si>
+    <t>BLOQUEOS</t>
+  </si>
+  <si>
     <t>AFORO</t>
   </si>
   <si>
-    <t>VENDIDOS</t>
-  </si>
-  <si>
-    <t>PROMOS</t>
-  </si>
-  <si>
-    <t>CORTESÍAS</t>
-  </si>
-  <si>
-    <t>PRECIO $1</t>
-  </si>
-  <si>
-    <t>ABONOS VENDIDOS</t>
-  </si>
-  <si>
-    <t>ABONOS PROMOS</t>
-  </si>
-  <si>
-    <t>ABONOS CORTESÍAS</t>
-  </si>
-  <si>
-    <t>ABONOS PRECIO $1</t>
-  </si>
-  <si>
-    <t>PAQUETES</t>
-  </si>
-  <si>
-    <t>PAQUETES CORTESIAS</t>
-  </si>
-  <si>
-    <t>PAQUETES PRECIO $1</t>
-  </si>
-  <si>
-    <t>BLOQUEOS</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>OCUPADOS</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -193,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -210,11 +213,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,11 +567,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="18" width="25" customWidth="1"/>
+    <col min="2" max="19" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -582,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -637,565 +649,598 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7">
+        <v>47</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7">
+        <v>263</v>
+      </c>
+      <c r="L6" s="7">
+        <v>15</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="7">
+        <v>125</v>
+      </c>
+      <c r="P6" s="7">
         <v>1887</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6">
-        <v>47</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6">
-        <v>263</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="Q6" s="7">
+        <v>450</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1437</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20</v>
+      </c>
+      <c r="L7" s="7">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="7">
+        <v>30</v>
+      </c>
+      <c r="P7" s="7">
+        <v>3300</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>56</v>
+      </c>
+      <c r="R7" s="7">
+        <v>3244</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="7">
+        <v>3</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="7">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="7">
+        <v>50</v>
+      </c>
+      <c r="P8" s="7">
+        <v>1027</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>61</v>
+      </c>
+      <c r="R8" s="7">
+        <v>966</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="7">
+        <v>84</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="7">
+        <v>14</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P10" s="7">
+        <v>78</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>14</v>
+      </c>
+      <c r="R10" s="7">
+        <v>64</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="7">
+        <v>50</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="7">
+        <v>54</v>
+      </c>
+      <c r="P11" s="7">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>104</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="7">
+        <v>3</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="7">
+        <v>12</v>
+      </c>
+      <c r="P12" s="7">
+        <v>60</v>
+      </c>
+      <c r="Q12" s="7">
         <v>15</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="6">
-        <v>125</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="6">
-        <v>450</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1437</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6">
-        <v>3300</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6">
-        <v>3</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="6">
-        <v>20</v>
-      </c>
-      <c r="L7" s="6">
-        <v>3</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="6">
+      <c r="R12" s="7">
+        <v>45</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="7">
+        <v>23</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="7">
+        <v>12</v>
+      </c>
+      <c r="P13" s="7">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>35</v>
+      </c>
+      <c r="R13" s="7">
+        <v>19</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="7">
         <v>30</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="6">
-        <v>56</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>3244</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="6">
-        <v>1027</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6">
-        <v>3</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="6">
-        <v>7</v>
-      </c>
-      <c r="L8" s="6">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="6">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="6">
-        <v>61</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>966</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6">
-        <v>84</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>84</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>78</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="6">
-        <v>14</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="6">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>64</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="6">
-        <v>104</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="6">
-        <v>50</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="6">
-        <v>54</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="6">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="H14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="7">
+        <v>6</v>
+      </c>
+      <c r="P14" s="7">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>36</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="6">
-        <v>60</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="6">
-        <v>3</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="6">
-        <v>12</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>45</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="6">
-        <v>54</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6">
-        <v>23</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6">
-        <v>12</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="6">
-        <v>35</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>19</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="6">
-        <v>36</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="6">
-        <v>6</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="6">
-        <v>36</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="7">
+        <v>40</v>
+      </c>
+      <c r="B15" s="9">
         <f>SUM(B6:B14)</f>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="9">
         <f>SUM(C6:C14)</f>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="9">
         <f>SUM(D6:D14)</f>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="9">
         <f>SUM(E6:E14)</f>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="9">
         <f>SUM(F6:F14)</f>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <f>SUM(G6:G14)</f>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <f>SUM(H6:H14)</f>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="9">
         <f>SUM(I6:I14)</f>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="9">
         <f>SUM(J6:J14)</f>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="9">
         <f>SUM(K6:K14)</f>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="9">
         <f>SUM(L6:L14)</f>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="9">
         <f>SUM(M6:M14)</f>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="9">
         <f>SUM(N6:N14)</f>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="9">
         <f>SUM(O6:O14)</f>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="9">
         <f>SUM(P6:P14)</f>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="9">
         <f>SUM(Q6:Q14)</f>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>40</v>
+      <c r="R15" s="9">
+        <f>SUM(R6:R14)</f>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,31 +82,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>41.18%</t>
+    <t>97.72%</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>1.70%</t>
+    <t>6.09%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
   </si>
   <si>
-    <t>21.32%</t>
+    <t>50.05%</t>
   </si>
   <si>
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>30.95%</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>17.95%</t>
+    <t>55.13%</t>
   </si>
   <si>
     <t>Palco Oro</t>
@@ -118,13 +118,13 @@
     <t>Palco Plata 1ra</t>
   </si>
   <si>
-    <t>30.00%</t>
+    <t>98.33%</t>
   </si>
   <si>
     <t>Palco Plata 3ra</t>
   </si>
   <si>
-    <t>94.44%</t>
+    <t>96.30%</t>
   </si>
   <si>
     <t>Palco Platino</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>19.23%</t>
+    <t>43.42%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +646,13 @@
         <v>1887</v>
       </c>
       <c r="C6" s="6">
-        <v>151</v>
+        <v>1202</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -670,7 +670,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="6">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L6" s="6">
         <v>16</v>
@@ -679,16 +679,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>225</v>
-      </c>
-      <c r="O6" s="6">
-        <v>38</v>
+        <v>266</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>777</v>
+        <v>1844</v>
       </c>
       <c r="Q6" s="6">
-        <v>1110</v>
+        <v>43</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -701,8 +701,8 @@
       <c r="B7" s="6">
         <v>3300</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+      <c r="C7" s="6">
+        <v>120</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -726,7 +726,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L7" s="6">
         <v>3</v>
@@ -735,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>56</v>
+        <v>201</v>
       </c>
       <c r="Q7" s="6">
-        <v>3244</v>
+        <v>3099</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>1027</v>
       </c>
       <c r="C8" s="6">
-        <v>7</v>
+        <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -782,7 +782,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L8" s="6">
         <v>1</v>
@@ -791,16 +791,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>200</v>
-      </c>
-      <c r="O8" s="6">
-        <v>1</v>
+        <v>280</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="Q8" s="6">
-        <v>808</v>
+        <v>513</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -813,8 +813,8 @@
       <c r="B9" s="6">
         <v>84</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="6">
+        <v>26</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -852,11 +852,11 @@
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>22</v>
+      <c r="P9" s="6">
+        <v>26</v>
       </c>
       <c r="Q9" s="6">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -869,8 +869,8 @@
       <c r="B10" s="6">
         <v>78</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
+      <c r="C10" s="6">
+        <v>24</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -894,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>22</v>
@@ -909,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="6">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -981,8 +981,8 @@
       <c r="B12" s="6">
         <v>60</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
+      <c r="C12" s="6">
+        <v>41</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="6">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1037,8 +1037,8 @@
       <c r="B13" s="6">
         <v>54</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
+      <c r="C13" s="6">
+        <v>7</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1073,14 +1073,14 @@
       <c r="N13" s="6">
         <v>12</v>
       </c>
-      <c r="O13" s="6">
-        <v>6</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q13" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,31 +82,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>97.72%</t>
+    <t>99.47%</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>6.09%</t>
+    <t>9.36%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
   </si>
   <si>
-    <t>50.05%</t>
+    <t>77.60%</t>
   </si>
   <si>
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>30.95%</t>
+    <t>64.29%</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>55.13%</t>
+    <t>67.95%</t>
   </si>
   <si>
     <t>Palco Oro</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>43.42%</t>
+    <t>50.39%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +646,13 @@
         <v>1887</v>
       </c>
       <c r="C6" s="6">
-        <v>1202</v>
+        <v>1235</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -679,16 +679,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1844</v>
+        <v>1877</v>
       </c>
       <c r="Q6" s="6">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,13 +702,13 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -741,10 +741,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="Q7" s="6">
-        <v>3099</v>
+        <v>2991</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>1027</v>
       </c>
       <c r="C8" s="6">
-        <v>219</v>
+        <v>493</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -775,14 +775,14 @@
       <c r="H8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>22</v>
+      <c r="I8" s="6">
+        <v>10</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L8" s="6">
         <v>1</v>
@@ -791,16 +791,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>280</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+        <v>270</v>
+      </c>
+      <c r="O8" s="6">
+        <v>4</v>
       </c>
       <c r="P8" s="6">
-        <v>514</v>
+        <v>797</v>
       </c>
       <c r="Q8" s="6">
-        <v>513</v>
+        <v>230</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -814,7 +814,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="6">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -853,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="6">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,7 +870,7 @@
         <v>78</v>
       </c>
       <c r="C10" s="6">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -909,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="43">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,31 +82,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>99.47%</t>
+    <t>99.95%</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>9.36%</t>
+    <t>13.94%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
   </si>
   <si>
-    <t>77.60%</t>
+    <t>99.32%</t>
   </si>
   <si>
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>64.29%</t>
+    <t>88.10%</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>67.95%</t>
+    <t>92.31%</t>
   </si>
   <si>
     <t>Palco Oro</t>
@@ -130,10 +130,16 @@
     <t>Palco Platino</t>
   </si>
   <si>
+    <t>Suites</t>
+  </si>
+  <si>
+    <t>28.32%</t>
+  </si>
+  <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>50.39%</t>
+    <t>56.28%</t>
   </si>
 </sst>
 </file>
@@ -555,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -646,13 +652,13 @@
         <v>1887</v>
       </c>
       <c r="C6" s="6">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -663,8 +669,8 @@
       <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
+      <c r="I6" s="6">
+        <v>129</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>22</v>
@@ -679,16 +685,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="Q6" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +708,7 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -719,14 +725,14 @@
       <c r="H7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
+      <c r="I7" s="6">
+        <v>30</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7" s="6">
         <v>3</v>
@@ -735,16 +741,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>309</v>
+        <v>460</v>
       </c>
       <c r="Q7" s="6">
-        <v>2991</v>
+        <v>2840</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,7 +764,7 @@
         <v>1027</v>
       </c>
       <c r="C8" s="6">
-        <v>493</v>
+        <v>769</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -776,7 +782,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -791,16 +797,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="O8" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P8" s="6">
-        <v>797</v>
+        <v>1020</v>
       </c>
       <c r="Q8" s="6">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -814,7 +820,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="6">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -853,10 +859,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="Q9" s="6">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,7 +876,7 @@
         <v>78</v>
       </c>
       <c r="C10" s="6">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -894,7 +900,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>22</v>
@@ -909,10 +915,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -943,8 +949,8 @@
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
+      <c r="I11" s="6">
+        <v>36</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -959,7 +965,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -1055,8 +1061,8 @@
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>12</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1070,8 +1076,8 @@
       <c r="M13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="6">
-        <v>12</v>
+      <c r="N13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1143,63 +1149,119 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>113</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6">
+        <v>32</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>81</v>
+      </c>
+      <c r="R15" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7">
+        <f>SUM(B6:B15)</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C6:C15)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D6:D15)</f>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E6:E15)</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F6:F15)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G6:G15)</f>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(H6:H15)</f>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(I6:I15)</f>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM(J6:J15)</f>
+      </c>
+      <c r="K16" s="7">
+        <f>SUM(K6:K15)</f>
+      </c>
+      <c r="L16" s="7">
+        <f>SUM(L6:L15)</f>
+      </c>
+      <c r="M16" s="7">
+        <f>SUM(M6:M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N6:N15)</f>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O6:O15)</f>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(P6:P15)</f>
+      </c>
+      <c r="Q16" s="7">
+        <f>SUM(Q6:Q15)</f>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,51 +82,39 @@
     <t>-</t>
   </si>
   <si>
-    <t>99.95%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>13.94%</t>
+    <t>24.21%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
   </si>
   <si>
-    <t>99.32%</t>
-  </si>
-  <si>
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>88.10%</t>
+    <t>96.43%</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>92.31%</t>
+    <t>97.44%</t>
   </si>
   <si>
     <t>Palco Oro</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Palco Plata 1ra</t>
   </si>
   <si>
-    <t>98.33%</t>
-  </si>
-  <si>
     <t>Palco Plata 3ra</t>
   </si>
   <si>
-    <t>96.30%</t>
-  </si>
-  <si>
     <t>Palco Platino</t>
   </si>
   <si>
@@ -139,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>56.28%</t>
+    <t>61.63%</t>
   </si>
 </sst>
 </file>
@@ -652,7 +640,7 @@
         <v>1887</v>
       </c>
       <c r="C6" s="6">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -685,16 +673,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1886</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
+        <v>1887</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -708,7 +696,7 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>376</v>
+        <v>705</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -732,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L7" s="6">
         <v>3</v>
@@ -743,14 +731,14 @@
       <c r="N7" s="6">
         <v>20</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>6</v>
       </c>
       <c r="P7" s="6">
-        <v>460</v>
+        <v>799</v>
       </c>
       <c r="Q7" s="6">
-        <v>2840</v>
+        <v>2501</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -764,7 +752,7 @@
         <v>1027</v>
       </c>
       <c r="C8" s="6">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -799,28 +787,28 @@
       <c r="N8" s="6">
         <v>160</v>
       </c>
-      <c r="O8" s="6">
-        <v>1</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1020</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>7</v>
+        <v>1027</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
         <v>84</v>
       </c>
       <c r="C9" s="6">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -859,18 +847,18 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q9" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>78</v>
@@ -900,7 +888,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>22</v>
@@ -911,22 +899,22 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>2</v>
       </c>
       <c r="P10" s="6">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>104</v>
@@ -977,12 +965,12 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>60</v>
@@ -1023,28 +1011,28 @@
       <c r="N12" s="6">
         <v>12</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+      <c r="O12" s="6">
+        <v>1</v>
       </c>
       <c r="P12" s="6">
-        <v>59</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>54</v>
       </c>
       <c r="C13" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1083,18 +1071,18 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>52</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>2</v>
+        <v>54</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6">
         <v>36</v>
@@ -1145,12 +1133,12 @@
         <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <v>113</v>
@@ -1201,12 +1189,12 @@
         <v>81</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1257,7 +1245,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,7 +88,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>24.21%</t>
+    <t>30.12%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
@@ -97,7 +97,7 @@
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>96.43%</t>
+    <t>98.81%</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
@@ -112,6 +112,9 @@
     <t>Palco Plata 1ra</t>
   </si>
   <si>
+    <t>98.33%</t>
+  </si>
+  <si>
     <t>Palco Plata 3ra</t>
   </si>
   <si>
@@ -127,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.63%</t>
+    <t>64.54%</t>
   </si>
 </sst>
 </file>
@@ -696,7 +699,7 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>705</v>
+        <v>903</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -732,13 +735,13 @@
         <v>20</v>
       </c>
       <c r="O7" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P7" s="6">
-        <v>799</v>
+        <v>994</v>
       </c>
       <c r="Q7" s="6">
-        <v>2501</v>
+        <v>2306</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -808,7 +811,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="6">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -847,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -864,7 +867,7 @@
         <v>78</v>
       </c>
       <c r="C10" s="6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -899,8 +902,8 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6">
-        <v>2</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
         <v>76</v>
@@ -1011,22 +1014,22 @@
       <c r="N12" s="6">
         <v>12</v>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="6">
+        <v>59</v>
+      </c>
+      <c r="Q12" s="6">
         <v>1</v>
       </c>
-      <c r="P12" s="6">
-        <v>60</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="R12" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>54</v>
@@ -1082,7 +1085,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>36</v>
@@ -1138,7 +1141,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6">
         <v>113</v>
@@ -1189,12 +1192,12 @@
         <v>81</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1245,7 +1248,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,7 +88,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>30.12%</t>
+    <t>35.91%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
@@ -103,7 +103,7 @@
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>97.44%</t>
+    <t>98.72%</t>
   </si>
   <si>
     <t>Palco Oro</t>
@@ -112,9 +112,6 @@
     <t>Palco Plata 1ra</t>
   </si>
   <si>
-    <t>98.33%</t>
-  </si>
-  <si>
     <t>Palco Plata 3ra</t>
   </si>
   <si>
@@ -130,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>64.54%</t>
+    <t>67.43%</t>
   </si>
 </sst>
 </file>
@@ -699,13 +696,13 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>903</v>
+        <v>1061</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -735,13 +732,13 @@
         <v>20</v>
       </c>
       <c r="O7" s="6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P7" s="6">
-        <v>994</v>
+        <v>1185</v>
       </c>
       <c r="Q7" s="6">
-        <v>2306</v>
+        <v>2115</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -760,8 +757,8 @@
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>10</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -788,7 +785,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -902,14 +899,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>1</v>
       </c>
       <c r="P10" s="6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -979,7 +976,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,18 +1015,18 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>59</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>54</v>
@@ -1085,10 +1082,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>22</v>
@@ -1096,8 +1093,8 @@
       <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
+      <c r="E14" s="6">
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1130,7 +1127,7 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
@@ -1141,7 +1138,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <v>113</v>
@@ -1192,12 +1189,12 @@
         <v>81</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1248,7 +1245,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="38">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,7 +88,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>35.91%</t>
+    <t>47.48%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
@@ -97,9 +97,6 @@
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
-    <t>98.81%</t>
-  </si>
-  <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
@@ -127,7 +124,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>67.43%</t>
+    <t>73.11%</t>
   </si>
 </sst>
 </file>
@@ -696,13 +693,13 @@
         <v>3300</v>
       </c>
       <c r="C7" s="6">
-        <v>1061</v>
+        <v>1432</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -732,13 +729,13 @@
         <v>20</v>
       </c>
       <c r="O7" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P7" s="6">
-        <v>1185</v>
+        <v>1567</v>
       </c>
       <c r="Q7" s="6">
-        <v>2115</v>
+        <v>1733</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -808,7 +805,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -847,24 +844,24 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>83</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>78</v>
       </c>
       <c r="C10" s="6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -899,8 +896,8 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6">
-        <v>1</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
         <v>77</v>
@@ -909,12 +906,12 @@
         <v>1</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>104</v>
@@ -970,7 +967,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>60</v>
@@ -1026,7 +1023,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>54</v>
@@ -1082,7 +1079,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6">
         <v>42</v>
@@ -1138,7 +1135,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6">
         <v>113</v>
@@ -1189,12 +1186,12 @@
         <v>81</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1245,7 +1242,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -76,19 +76,25 @@
     <t>% OCUPACIÓN</t>
   </si>
   <si>
+    <t>Acceso</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
     <t>Central</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>100.00%</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>47.48%</t>
+    <t>67.88%</t>
   </si>
   <si>
     <t>Lateral Preferente</t>
@@ -124,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>73.11%</t>
+    <t>77.35%</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -634,52 +640,52 @@
         <v>21</v>
       </c>
       <c r="B6" s="6">
-        <v>1887</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1246</v>
+        <v>500</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6">
-        <v>43</v>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="6">
-        <v>47</v>
+      <c r="G6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="6">
-        <v>129</v>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="6">
-        <v>295</v>
-      </c>
-      <c r="L6" s="6">
-        <v>16</v>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>111</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="6">
-        <v>1887</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>22</v>
+      <c r="P6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>500</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -690,52 +696,52 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>3300</v>
+        <v>1887</v>
       </c>
       <c r="C7" s="6">
-        <v>1432</v>
+        <v>1246</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="6">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>31</v>
+        <v>295</v>
       </c>
       <c r="L7" s="6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>20</v>
-      </c>
-      <c r="O7" s="6">
-        <v>13</v>
+        <v>101</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1567</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>1733</v>
+        <v>1887</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -746,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>1027</v>
+        <v>3300</v>
       </c>
       <c r="C8" s="6">
-        <v>777</v>
+        <v>1959</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -767,101 +773,101 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="L8" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>150</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="O8" s="6">
+        <v>17</v>
       </c>
       <c r="P8" s="6">
-        <v>1027</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>22</v>
+        <v>2240</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1060</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>84</v>
+        <v>1027</v>
       </c>
       <c r="C9" s="6">
-        <v>84</v>
+        <v>777</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>10</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>22</v>
+      <c r="G9" s="6">
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
+      <c r="I9" s="6">
+        <v>70</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
+      <c r="K9" s="6">
+        <v>16</v>
+      </c>
+      <c r="L9" s="6">
+        <v>1</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
+      <c r="N9" s="6">
+        <v>150</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>84</v>
+        <v>1027</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C10" s="6">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -884,7 +890,7 @@
       <c r="J10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="6" t="s">
@@ -900,13 +906,13 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>77</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -914,10 +920,10 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>104</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="C11" s="6">
+        <v>55</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -928,19 +934,19 @@
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="6">
-        <v>50</v>
+      <c r="G11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>36</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="6">
         <v>22</v>
       </c>
       <c r="L11" s="6" t="s">
@@ -949,55 +955,55 @@
       <c r="M11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="6">
-        <v>18</v>
+      <c r="N11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>1</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
-        <v>60</v>
-      </c>
-      <c r="C12" s="6">
+        <v>104</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="6">
         <v>42</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="6">
-        <v>6</v>
+      <c r="K12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>22</v>
@@ -1012,24 +1018,24 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C13" s="6">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1046,207 +1052,263 @@
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6">
         <v>12</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6">
-        <v>33</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="6">
+        <v>54</v>
+      </c>
+      <c r="C14" s="6">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="6">
+        <v>12</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6">
         <v>33</v>
       </c>
-      <c r="B14" s="6">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6">
-        <v>6</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="L14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="6">
-        <v>6</v>
+      <c r="N14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
+        <v>42</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6">
+        <v>6</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6">
+        <v>30</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6">
+        <v>6</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6">
         <v>113</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="6">
+      <c r="C16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="6">
         <v>32</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="6">
+      <c r="J16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="6">
         <v>32</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="Q16" s="6">
         <v>81</v>
       </c>
-      <c r="R15" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="7">
-        <f>SUM(B6:B15)</f>
-      </c>
-      <c r="C16" s="7">
-        <f>SUM(C6:C15)</f>
-      </c>
-      <c r="D16" s="7">
-        <f>SUM(D6:D15)</f>
-      </c>
-      <c r="E16" s="7">
-        <f>SUM(E6:E15)</f>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F6:F15)</f>
-      </c>
-      <c r="G16" s="7">
-        <f>SUM(G6:G15)</f>
-      </c>
-      <c r="H16" s="7">
-        <f>SUM(H6:H15)</f>
-      </c>
-      <c r="I16" s="7">
-        <f>SUM(I6:I15)</f>
-      </c>
-      <c r="J16" s="7">
-        <f>SUM(J6:J15)</f>
-      </c>
-      <c r="K16" s="7">
-        <f>SUM(K6:K15)</f>
-      </c>
-      <c r="L16" s="7">
-        <f>SUM(L6:L15)</f>
-      </c>
-      <c r="M16" s="7">
-        <f>SUM(M6:M15)</f>
-      </c>
-      <c r="N16" s="7">
-        <f>SUM(N6:N15)</f>
-      </c>
-      <c r="O16" s="7">
-        <f>SUM(O6:O15)</f>
-      </c>
-      <c r="P16" s="7">
-        <f>SUM(P6:P15)</f>
-      </c>
-      <c r="Q16" s="7">
-        <f>SUM(Q6:Q15)</f>
-      </c>
-      <c r="R16" s="7" t="s">
+      <c r="R16" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7">
+        <f>SUM(B6:B16)</f>
+      </c>
+      <c r="C17" s="7">
+        <f>SUM(C6:C16)</f>
+      </c>
+      <c r="D17" s="7">
+        <f>SUM(D6:D16)</f>
+      </c>
+      <c r="E17" s="7">
+        <f>SUM(E6:E16)</f>
+      </c>
+      <c r="F17" s="7">
+        <f>SUM(F6:F16)</f>
+      </c>
+      <c r="G17" s="7">
+        <f>SUM(G6:G16)</f>
+      </c>
+      <c r="H17" s="7">
+        <f>SUM(H6:H16)</f>
+      </c>
+      <c r="I17" s="7">
+        <f>SUM(I6:I16)</f>
+      </c>
+      <c r="J17" s="7">
+        <f>SUM(J6:J16)</f>
+      </c>
+      <c r="K17" s="7">
+        <f>SUM(K6:K16)</f>
+      </c>
+      <c r="L17" s="7">
+        <f>SUM(L6:L16)</f>
+      </c>
+      <c r="M17" s="7">
+        <f>SUM(M6:M16)</f>
+      </c>
+      <c r="N17" s="7">
+        <f>SUM(N6:N16)</f>
+      </c>
+      <c r="O17" s="7">
+        <f>SUM(O6:O16)</f>
+      </c>
+      <c r="P17" s="7">
+        <f>SUM(P6:P16)</f>
+      </c>
+      <c r="Q17" s="7">
+        <f>SUM(Q6:Q16)</f>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Caliente 2026.xlsx
+++ b/data/asistencia/Caliente 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,36 +82,39 @@
     <t>-</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>4.00%</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
+    <t>99.89%</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+  </si>
+  <si>
+    <t>98.85%</t>
+  </si>
+  <si>
+    <t>Lateral Preferente</t>
+  </si>
+  <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>Lateral</t>
-  </si>
-  <si>
-    <t>67.88%</t>
-  </si>
-  <si>
-    <t>Lateral Preferente</t>
-  </si>
-  <si>
     <t>Palco Bronce 1ra</t>
   </si>
   <si>
     <t>Palco Bronce 3ra</t>
   </si>
   <si>
-    <t>98.72%</t>
-  </si>
-  <si>
     <t>Palco Oro</t>
   </si>
   <si>
+    <t>105.77%</t>
+  </si>
+  <si>
     <t>Palco Plata 1ra</t>
   </si>
   <si>
@@ -124,13 +127,13 @@
     <t>Suites</t>
   </si>
   <si>
-    <t>28.32%</t>
+    <t>42.48%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>77.35%</t>
+    <t>92.01%</t>
   </si>
 </sst>
 </file>
@@ -648,8 +651,8 @@
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
+      <c r="E6" s="6">
+        <v>20</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -681,11 +684,11 @@
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>22</v>
+      <c r="P6" s="6">
+        <v>20</v>
       </c>
       <c r="Q6" s="6">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -705,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -726,22 +729,22 @@
         <v>295</v>
       </c>
       <c r="L7" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1887</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>22</v>
+        <v>1885</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,13 +758,13 @@
         <v>3300</v>
       </c>
       <c r="C8" s="6">
-        <v>1959</v>
+        <v>2434</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -788,16 +791,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>20</v>
-      </c>
-      <c r="O8" s="6">
-        <v>17</v>
+        <v>551</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>2240</v>
+        <v>3262</v>
       </c>
       <c r="Q8" s="6">
-        <v>1060</v>
+        <v>38</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -856,12 +859,12 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6">
         <v>84</v>
@@ -912,18 +915,18 @@
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>78</v>
       </c>
       <c r="C11" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -962,13 +965,13 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>77</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1012,24 +1015,24 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>60</v>
@@ -1080,12 +1083,12 @@
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>54</v>
@@ -1136,12 +1139,12 @@
         <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6">
         <v>42</v>
@@ -1192,12 +1195,12 @@
         <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6">
         <v>113</v>
@@ -1208,8 +1211,8 @@
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>22</v>
+      <c r="E16" s="6">
+        <v>16</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1242,18 +1245,18 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="6">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="7">
         <f>SUM(B6:B16)</f>
@@ -1304,7 +1307,7 @@
         <f>SUM(Q6:Q16)</f>
       </c>
       <c r="R17" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
